--- a/artfynd/A 36672-2023 artfynd.xlsx
+++ b/artfynd/A 36672-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36672-2023 artfynd.xlsx
+++ b/artfynd/A 36672-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97578164</v>
+        <v>97578142</v>
       </c>
       <c r="B2" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592760.339167145</v>
+        <v>592757</v>
       </c>
       <c r="R2" t="n">
-        <v>6727210.975408638</v>
+        <v>6727209</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97578407</v>
+        <v>97578144</v>
       </c>
       <c r="B3" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,38 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>100141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Jäderfors, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592814.4904397819</v>
+        <v>592815</v>
       </c>
       <c r="R3" t="n">
-        <v>6727130.000448878</v>
+        <v>6727135</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,19 +845,9 @@
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -913,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97578390</v>
+        <v>97578164</v>
       </c>
       <c r="B4" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>100141</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592759.2689766206</v>
+        <v>592761</v>
       </c>
       <c r="R4" t="n">
-        <v>6727214.379986852</v>
+        <v>6727211</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1030,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97578144</v>
+        <v>97578393</v>
       </c>
       <c r="B5" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592815.3453509193</v>
+        <v>592781</v>
       </c>
       <c r="R5" t="n">
-        <v>6727134.92584958</v>
+        <v>6727198</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,19 +1049,9 @@
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1150,12 +1086,7 @@
         <v>97578395</v>
       </c>
       <c r="B6" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592809.4304827568</v>
+        <v>592809</v>
       </c>
       <c r="R6" t="n">
-        <v>6727135.75359766</v>
+        <v>6727136</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,19 +1155,9 @@
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1268,15 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97578393</v>
+        <v>97578158</v>
       </c>
       <c r="B7" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1308,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592780.3377598217</v>
+        <v>592836</v>
       </c>
       <c r="R7" t="n">
-        <v>6727197.272916029</v>
+        <v>6727128</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,22 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1385,15 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97578142</v>
+        <v>97578160</v>
       </c>
       <c r="B8" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592757.4451033045</v>
+        <v>592761</v>
       </c>
       <c r="R8" t="n">
-        <v>6727208.939356862</v>
+        <v>6727192</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,22 +1356,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1505,12 +1396,7 @@
         <v>97578388</v>
       </c>
       <c r="B9" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592750.510827159</v>
+        <v>592750</v>
       </c>
       <c r="R9" t="n">
-        <v>6727211.211794445</v>
+        <v>6727211</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1575,19 +1461,9 @@
           <t>2021-05-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-05-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1619,15 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97578158</v>
+        <v>97578390</v>
       </c>
       <c r="B10" t="n">
-        <v>57585</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592836.1487794233</v>
+        <v>592760</v>
       </c>
       <c r="R10" t="n">
-        <v>6727128.108783737</v>
+        <v>6727214</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1689,22 +1560,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1736,15 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97578162</v>
+        <v>97578407</v>
       </c>
       <c r="B11" t="n">
-        <v>57585</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,34 +1608,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208242</v>
+        <v>208250</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Jäderfors, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592760.8202666106</v>
+        <v>592814</v>
       </c>
       <c r="R11" t="n">
-        <v>6727192.355677384</v>
+        <v>6727130</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1806,22 +1666,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 36672-2023 artfynd.xlsx
+++ b/artfynd/A 36672-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578144</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578164</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578395</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578158</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578388</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578390</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,8 +1750,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97578407</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>